--- a/CDF Batt Cap/SplineCDF_Fall2025_Batt Cap.xlsx
+++ b/CDF Batt Cap/SplineCDF_Fall2025_Batt Cap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF Batt Cap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C27AAB8-D0B0-407F-BBDF-E897E32194BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{5C27AAB8-D0B0-407F-BBDF-E897E32194BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D0F3DD5-C6DE-4445-9F4D-519BBAE34BEB}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6544,127 +6544,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>1</v>
+        <v>0.19238611002525399</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.3</v>
+        <v>9.8573270641918162E-2</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.3</v>
+        <v>0.105</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>-4.9999999999999989E-2</v>
+        <v>-0.15311111111111114</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>0</v>
+        <v>0.2484444444444445</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.14999999999999997</v>
+        <v>3.4666666666666658E-2</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-9.9999999999999978E-2</v>
+        <v>-7.2386110025253997E-2</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K2" t="e">
+        <v>2.0880608661130964</v>
+      </c>
+      <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L2" t="e">
+        <v>0.47449795856387667</v>
+      </c>
+      <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>#DIV/0!</v>
+        <v>0.47449795856387667</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>-3</v>
+        <v>-1.104070250385665</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>2</v>
+        <v>3.3833946248789104E-2</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>0</v>
+        <v>-4.9559362213923958E-2</v>
       </c>
       <c r="P2">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>1</v>
+        <v>0.2232611614088206</v>
       </c>
       <c r="Q2">
         <f ca="1">P2^(1/3)</f>
-        <v>1</v>
+        <v>0.60664933593899339</v>
       </c>
       <c r="R2">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>3.1415926535897931</v>
+        <v>1.6466411485242713</v>
       </c>
       <c r="S2">
         <f ca="1">-Q2</f>
-        <v>-1</v>
+        <v>-0.60664933593899339</v>
       </c>
       <c r="T2">
         <f ca="1">COS(R2/3)</f>
-        <v>0.50000000000000011</v>
+        <v>0.85310919718948153</v>
       </c>
       <c r="U2">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>1.4999999999999998</v>
+        <v>0.90366702551999467</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>0</v>
+        <v>0.54088050314465408</v>
       </c>
       <c r="W2">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>1.0000000000000002</v>
+        <v>1.5759567590615475</v>
       </c>
       <c r="X2">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>-2</v>
+        <v>-0.52486662575546272</v>
       </c>
       <c r="Y2">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>0.99999999999999967</v>
-      </c>
-      <c r="Z2">
+        <v>0.57155137612787754</v>
+      </c>
+      <c r="Z2" t="e">
         <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>-1</v>
-      </c>
-      <c r="AA2">
+        <v>#NUM!</v>
+      </c>
+      <c r="AA2" t="e">
         <f ca="1">Z2^(1/3)</f>
-        <v>-1</v>
-      </c>
-      <c r="AB2">
+        <v>#NUM!</v>
+      </c>
+      <c r="AB2" t="e">
         <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>-1</v>
-      </c>
-      <c r="AC2">
+        <v>#NUM!</v>
+      </c>
+      <c r="AC2" t="e">
         <f ca="1">AB2^(1/3)</f>
-        <v>-1</v>
-      </c>
-      <c r="AD2">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD2" t="e">
         <f ca="1">AA2+AC2+V2</f>
-        <v>-2</v>
+        <v>#NUM!</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>1.0000000000000002</v>
+        <v>0.57155137612787754</v>
       </c>
       <c r="AG2" t="s">
         <v>40</v>
@@ -36498,12 +36498,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36641,6 +36635,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -36651,15 +36651,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8464FFB8-1CA5-473B-A7BB-16B579D11E9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{640F626E-530A-4DD9-ABC5-8AC4E7F98173}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36677,6 +36668,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8464FFB8-1CA5-473B-A7BB-16B579D11E9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E05344D-D20F-4130-99B5-ABD77F574CE3}">
   <ds:schemaRefs>

--- a/CDF Batt Cap/SplineCDF_Fall2025_Batt Cap.xlsx
+++ b/CDF Batt Cap/SplineCDF_Fall2025_Batt Cap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF Batt Cap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{5C27AAB8-D0B0-407F-BBDF-E897E32194BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D0F3DD5-C6DE-4445-9F4D-519BBAE34BEB}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{5C27AAB8-D0B0-407F-BBDF-E897E32194BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E654A79-637D-47A9-8D5E-C3FEF3B79591}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4786,6 +4786,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6544,11 +6548,11 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.19238611002525399</v>
+        <v>0.17716129114785101</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>9.8573270641918162E-2</v>
+        <v>9.721904864099401E-2</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
@@ -6576,19 +6580,19 @@
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-7.2386110025253997E-2</v>
+        <v>-5.7161291147851012E-2</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>2.0880608661130964</v>
+        <v>1.6488833984957028</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.47449795856387667</v>
+        <v>0.41494303793363163</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.47449795856387667</v>
+        <v>0.41494303793363163</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
@@ -6596,11 +6600,11 @@
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>3.3833946248789104E-2</v>
+        <v>-6.5602461513639646E-2</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>-4.9559362213923958E-2</v>
+        <v>-4.8769625454453305E-2</v>
       </c>
       <c r="P2">
         <f ca="1">SQRT(N2^2/4-O2)</f>
@@ -6612,7 +6616,7 @@
       </c>
       <c r="R2">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>1.6466411485242713</v>
+        <v>1.4233439233972374</v>
       </c>
       <c r="S2">
         <f ca="1">-Q2</f>
@@ -6620,11 +6624,11 @@
       </c>
       <c r="T2">
         <f ca="1">COS(R2/3)</f>
-        <v>0.85310919718948153</v>
+        <v>0.88954504861292882</v>
       </c>
       <c r="U2">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>0.90366702551999467</v>
+        <v>0.79128302108958848</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
@@ -6632,15 +6636,15 @@
       </c>
       <c r="W2">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>1.5759567590615475</v>
+        <v>1.62016432920236</v>
       </c>
       <c r="X2">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>-0.52486662575546272</v>
+        <v>-0.4787927291679982</v>
       </c>
       <c r="Y2">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>0.57155137612787754</v>
+        <v>0.48126990939960057</v>
       </c>
       <c r="Z2" t="e">
         <f ca="1">-N2/2+SQRT(O2)</f>
@@ -6664,7 +6668,7 @@
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.57155137612787754</v>
+        <v>0.48126990939960057</v>
       </c>
       <c r="AG2" t="s">
         <v>40</v>
@@ -36498,6 +36502,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36635,12 +36645,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -36651,6 +36655,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8464FFB8-1CA5-473B-A7BB-16B579D11E9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{640F626E-530A-4DD9-ABC5-8AC4E7F98173}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36668,15 +36681,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8464FFB8-1CA5-473B-A7BB-16B579D11E9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E05344D-D20F-4130-99B5-ABD77F574CE3}">
   <ds:schemaRefs>

--- a/CDF Batt Cap/SplineCDF_Fall2025_Batt Cap.xlsx
+++ b/CDF Batt Cap/SplineCDF_Fall2025_Batt Cap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF Batt Cap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{5C27AAB8-D0B0-407F-BBDF-E897E32194BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E654A79-637D-47A9-8D5E-C3FEF3B79591}"/>
+  <xr:revisionPtr revIDLastSave="1354" documentId="13_ncr:1_{5C27AAB8-D0B0-407F-BBDF-E897E32194BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5CB0229-1F64-4C55-82B6-C99683F2F574}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6548,127 +6548,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.17716129114785101</v>
+        <v>0.25168625228466501</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>9.721904864099401E-2</v>
+        <v>0.10535534044861901</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.09</v>
+        <v>0.105</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.105</v>
+        <v>0.12</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>-0.15311111111111114</v>
+        <v>2.2222222222222185E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>0.2484444444444445</v>
+        <v>-4.4444444444444398E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>3.4666666666666658E-2</v>
+        <v>7.2222222222222202E-2</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-5.7161291147851012E-2</v>
+        <v>-1.686252284665013E-3</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>1.6488833984957028</v>
+        <v>2.3348108556900185E-2</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.41494303793363163</v>
+        <v>2.3693576601307623E-2</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.41494303793363163</v>
+        <v>2.3693576601307623E-2</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>-1.104070250385665</v>
+        <v>1.9166666666666696</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>-6.5602461513639646E-2</v>
+        <v>1.4981927212641517</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>-4.8769625454453305E-2</v>
-      </c>
-      <c r="P2">
+        <v>0.82192639317751715</v>
+      </c>
+      <c r="P2" t="e">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>0.2232611614088206</v>
-      </c>
-      <c r="Q2">
+        <v>#NUM!</v>
+      </c>
+      <c r="Q2" t="e">
         <f ca="1">P2^(1/3)</f>
-        <v>0.60664933593899339</v>
-      </c>
-      <c r="R2">
+        <v>#NUM!</v>
+      </c>
+      <c r="R2" t="e">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>1.4233439233972374</v>
-      </c>
-      <c r="S2">
+        <v>#NUM!</v>
+      </c>
+      <c r="S2" t="e">
         <f ca="1">-Q2</f>
-        <v>-0.60664933593899339</v>
-      </c>
-      <c r="T2">
+        <v>#NUM!</v>
+      </c>
+      <c r="T2" t="e">
         <f ca="1">COS(R2/3)</f>
-        <v>0.88954504861292882</v>
-      </c>
-      <c r="U2">
+        <v>#NUM!</v>
+      </c>
+      <c r="U2" t="e">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>0.79128302108958848</v>
+        <v>#NUM!</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>0.54088050314465408</v>
-      </c>
-      <c r="W2">
+        <v>0.66666666666666707</v>
+      </c>
+      <c r="W2" t="e">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>1.62016432920236</v>
-      </c>
-      <c r="X2">
+        <v>#NUM!</v>
+      </c>
+      <c r="X2" t="e">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>-0.4787927291679982</v>
-      </c>
-      <c r="Y2">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y2" t="e">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>0.48126990939960057</v>
-      </c>
-      <c r="Z2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z2">
         <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>0.1575052018955414</v>
+      </c>
+      <c r="AA2">
         <f ca="1">Z2^(1/3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB2" t="e">
+        <v>0.54004709453869015</v>
+      </c>
+      <c r="AB2">
         <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC2" t="e">
+        <v>-1.6556979231596931</v>
+      </c>
+      <c r="AC2">
         <f ca="1">AB2^(1/3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD2" t="e">
+        <v>-1.1830243979640898</v>
+      </c>
+      <c r="AD2">
         <f ca="1">AA2+AC2+V2</f>
-        <v>#NUM!</v>
+        <v>2.3689363241267469E-2</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.48126990939960057</v>
+        <v>2.3689363241267469E-2</v>
       </c>
       <c r="AG2" t="s">
         <v>40</v>
@@ -36502,9 +36502,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36646,19 +36649,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8464FFB8-1CA5-473B-A7BB-16B579D11E9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E05344D-D20F-4130-99B5-ABD77F574CE3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -36682,9 +36681,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E05344D-D20F-4130-99B5-ABD77F574CE3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8464FFB8-1CA5-473B-A7BB-16B579D11E9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>